--- a/KatalonData/RADTestData/BeforePaymentsCorp.xlsx
+++ b/KatalonData/RADTestData/BeforePaymentsCorp.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9828FF02-D57B-4323-8483-F339B8A0CA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{C62C7ED8-F369-4F4C-9058-5982C6F302E8}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="14303" yWindow="-2010" windowWidth="28995" windowHeight="15675" activeTab="6" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView activeTab="3" windowHeight="15675" windowWidth="28996" xWindow="-98" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-98"/>
   </bookViews>
   <sheets>
-    <sheet name="Estimated" sheetId="1" r:id="rId1"/>
-    <sheet name="Existing" sheetId="2" r:id="rId2"/>
-    <sheet name="Extension" sheetId="3" r:id="rId3"/>
-    <sheet name="NewTaxReturn" sheetId="4" r:id="rId4"/>
-    <sheet name="Personal_IND" sheetId="6" r:id="rId5"/>
-    <sheet name="Personal_JNT" sheetId="7" r:id="rId6"/>
-    <sheet name="Personal_EL" sheetId="8" r:id="rId7"/>
+    <sheet name="Estimated" r:id="rId1" sheetId="1"/>
+    <sheet name="Existing" r:id="rId2" sheetId="2"/>
+    <sheet name="Extension" r:id="rId3" sheetId="3"/>
+    <sheet name="NewTaxReturn" r:id="rId4" sheetId="4"/>
+    <sheet name="Personal_IND" r:id="rId5" sheetId="6"/>
+    <sheet name="Personal_JNT" r:id="rId6" sheetId="7"/>
+    <sheet name="Personal_EL" r:id="rId7" sheetId="8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NewTaxReturn!$E$1:$E$61</definedName>
+    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">NewTaxReturn!$E$1:$E$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="417">
   <si>
     <t>Result</t>
   </si>
@@ -134,9 +134,6 @@
     <t>Alcohol Tax</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
@@ -390,12 +387,922 @@
   </si>
   <si>
     <t>This is in QA and Demo but not in Production</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Sat May 23 12:59:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 12:59:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:00:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:00:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:01:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:02:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:02:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:03:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:03:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:04:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:04:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:05:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:05:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:06:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:06:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:07:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:08:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:08:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:09:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:09:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:10:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:10:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:11:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:11:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:12:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:12:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:13:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:13:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:14:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:14:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:15:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:15:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:16:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:16:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:17:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:17:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:18:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:19:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:19:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:20:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:20:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:21:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:21:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:22:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:22:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:23:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:23:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:24:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:24:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:25:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:25:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:26:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:26:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:27:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:27:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:28:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:28:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:29:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:30:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:30:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:31:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:31:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:32:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:32:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:33:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:33:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:34:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:35:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:35:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:36:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:36:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:37:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:37:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:38:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:38:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:39:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:40:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:40:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:41:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:41:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:42:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:42:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:43:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:43:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:44:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:44:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:45:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 13:45:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 14:36:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 14:36:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 14:37:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 14:37:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 14:38:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 14:39:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 14:39:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 14:40:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 14:40:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 14:41:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 14:41:51 EDT 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Fri May 29 12:36:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:37:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:38:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:39:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:39:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:40:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:40:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:42:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:42:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:43:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:43:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:44:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:44:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:45:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:46:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:46:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:47:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:47:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:48:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:48:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:49:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:49:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:50:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:50:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:51:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:52:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:53:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:54:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:54:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:55:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:55:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:56:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:57:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:57:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:58:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:58:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:59:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 12:59:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:00:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:00:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:01:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:01:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:02:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:03:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:03:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:04:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:04:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:05:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:05:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:06:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:06:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:07:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:08:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:08:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:09:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:10:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:10:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:11:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:12:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:12:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:13:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:13:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:14:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:14:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:15:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:15:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:16:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:16:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:17:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:18:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:18:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:19:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:19:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:20:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:21:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:23:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:24:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:25:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:26:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:27:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:28:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:30:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:31:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:32:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:33:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:35:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:37:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:38:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:40:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:42:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:43:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:44:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:46:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:47:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:48:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:49:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:50:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:51:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:53:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 13:54:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:22:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:23:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:25:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:26:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:27:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:28:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:29:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:31:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:32:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:33:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:35:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:36:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:37:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:38:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:39:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:40:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:42:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:43:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:44:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:45:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:46:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:47:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:48:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:50:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:51:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:52:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:54:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:55:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:56:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:58:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:59:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:00:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:01:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:03:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:04:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:05:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:06:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:07:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:08:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:10:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:11:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:13:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:14:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:15:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:16:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:17:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:19:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:20:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:21:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:22:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:23:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:24:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:26:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:27:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:28:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:29:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:30:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:32:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:33:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:35:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:36:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:37:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:38:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:39:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:40:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:41:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:43:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:44:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:45:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:46:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:47:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:49:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:50:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:51:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:52:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:53:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:54:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:55:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:57:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:58:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:59:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:00:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:01:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:02:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:04:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:06:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:07:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:09:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:11:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:12:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:14:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:15:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:16:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:17:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:18:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:20:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:21:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:22:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:23:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:25:11 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -444,19 +1351,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -473,10 +1380,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -511,7 +1418,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -563,7 +1470,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -674,21 +1581,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -705,7 +1612,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -757,31 +1664,31 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="44.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.1796875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="18.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -804,20 +1711,24 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>317</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
@@ -826,23 +1737,27 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>318</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>7</v>
@@ -851,23 +1766,27 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>319</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
@@ -876,26 +1795,30 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>320</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
@@ -904,26 +1827,30 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>321</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -932,26 +1859,30 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7"/>
-      <c r="B7"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>322</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>7</v>
@@ -960,25 +1891,48 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -986,23 +1940,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
-  <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.6328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.1796875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="16.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.1796875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="43.36328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1019,406 +1973,482 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>324</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>325</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>326</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>327</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>328</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7"/>
-      <c r="B7"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>329</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8"/>
-      <c r="B8"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" t="s">
+        <v>330</v>
+      </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9"/>
-      <c r="B9"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s">
+        <v>331</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10"/>
-      <c r="B10"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" t="s">
+        <v>332</v>
+      </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11"/>
-      <c r="B11"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" t="s">
+        <v>333</v>
+      </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12"/>
-      <c r="B12"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" t="s">
+        <v>334</v>
+      </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" t="s">
+        <v>335</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13"/>
-      <c r="B13"/>
-      <c r="C13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="1" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" t="s">
+        <v>336</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="C14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" s="1" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" t="s">
+        <v>337</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15"/>
-      <c r="B15"/>
-      <c r="C15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="1" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="F16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16"/>
-      <c r="B16"/>
-      <c r="C16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="1" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>339</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="1" t="s">
+      <c r="G17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17"/>
-      <c r="B17"/>
-      <c r="C17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" s="1" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" t="s">
+        <v>340</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="1" t="s">
+      <c r="F18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18"/>
-      <c r="B18"/>
-      <c r="C18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20"/>
-      <c r="B20"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" t="s">
+        <v>341</v>
+      </c>
       <c r="C20" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21"/>
-      <c r="B21"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>222</v>
+      </c>
+      <c r="B21" t="s">
+        <v>342</v>
+      </c>
       <c r="C21" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1426,22 +2456,22 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.1796875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1464,17 +2494,21 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>343</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
@@ -1483,20 +2517,24 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
@@ -1505,17 +2543,21 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>345</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>14</v>
@@ -1524,20 +2566,24 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>346</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>14</v>
@@ -1546,20 +2592,24 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>347</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>14</v>
@@ -1568,20 +2618,24 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7"/>
-      <c r="B7"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>348</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>14</v>
@@ -1590,18 +2644,18 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1609,23 +2663,23 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
-  <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
+  <dimension ref="A1:M61"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.1796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.7265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.7265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="41.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.1796875" style="1" collapsed="1"/>
-    <col min="7" max="10" width="19.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1796875" style="1" collapsed="1"/>
-    <col min="12" max="12" width="43.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="11" max="11" style="1" width="9.19921875" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
+    <col min="13" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1645,29 +2699,33 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>349</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>15</v>
@@ -1675,18 +2733,22 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1">
-        <v>2024</v>
+      <c r="F2" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>350</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>15</v>
@@ -1694,21 +2756,25 @@
       <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1">
-        <v>2024</v>
+      <c r="F3" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>351</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -1716,21 +2782,25 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1">
-        <v>2024</v>
+      <c r="F4" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>352</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
@@ -1738,21 +2808,25 @@
       <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="1">
-        <v>2024</v>
+      <c r="F5" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>353</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
@@ -1760,21 +2834,25 @@
       <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="1">
-        <v>2024</v>
+      <c r="F6" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7"/>
-      <c r="B7"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>354</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
@@ -1782,18 +2860,22 @@
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="1">
-        <v>2023</v>
+      <c r="F7" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8"/>
-      <c r="B8"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" t="s">
+        <v>355</v>
+      </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>15</v>
@@ -1801,21 +2883,25 @@
       <c r="E8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="1">
-        <v>2023</v>
+      <c r="F8" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9"/>
-      <c r="B9"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>15</v>
@@ -1823,21 +2909,25 @@
       <c r="E9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="1">
-        <v>2023</v>
+      <c r="F9" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10"/>
-      <c r="B10"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" t="s">
+        <v>357</v>
+      </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>15</v>
@@ -1845,21 +2935,25 @@
       <c r="E10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="1">
-        <v>2023</v>
+      <c r="F10" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11"/>
-      <c r="B11"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" t="s">
+        <v>358</v>
+      </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>15</v>
@@ -1867,21 +2961,25 @@
       <c r="E11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="1">
-        <v>2023</v>
+      <c r="F11" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12"/>
-      <c r="B12"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" t="s">
+        <v>359</v>
+      </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>15</v>
@@ -1889,18 +2987,22 @@
       <c r="E12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="1">
-        <v>2022</v>
+      <c r="F12" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13"/>
-      <c r="B13"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" t="s">
+        <v>360</v>
+      </c>
       <c r="C13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>15</v>
@@ -1908,21 +3010,25 @@
       <c r="E13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="1">
-        <v>2022</v>
+      <c r="F13" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14"/>
-      <c r="B14"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" t="s">
+        <v>361</v>
+      </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>15</v>
@@ -1930,21 +3036,25 @@
       <c r="E14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="1">
-        <v>2022</v>
+      <c r="F14" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15"/>
-      <c r="B15"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" t="s">
+        <v>362</v>
+      </c>
       <c r="C15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>15</v>
@@ -1952,21 +3062,25 @@
       <c r="E15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="1">
-        <v>2022</v>
+      <c r="F15" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16"/>
-      <c r="B16"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" t="s">
+        <v>363</v>
+      </c>
       <c r="C16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>15</v>
@@ -1974,46 +3088,54 @@
       <c r="E16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="1">
-        <v>2022</v>
+      <c r="F16" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>364</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17"/>
-      <c r="B17"/>
-      <c r="C17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18"/>
-      <c r="B18"/>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" t="s">
+        <v>365</v>
+      </c>
       <c r="C18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>15</v>
@@ -2021,24 +3143,28 @@
       <c r="E18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="1">
-        <v>2025</v>
+      <c r="F18" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19"/>
-      <c r="B19"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" t="s">
+        <v>366</v>
+      </c>
       <c r="C19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>15</v>
@@ -2046,24 +3172,28 @@
       <c r="E19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="1">
-        <v>2025</v>
+      <c r="F19" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20"/>
-      <c r="B20"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" t="s">
+        <v>367</v>
+      </c>
       <c r="C20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>15</v>
@@ -2071,90 +3201,106 @@
       <c r="E20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="1">
-        <v>2024</v>
+      <c r="F20" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="K20" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21"/>
-      <c r="B21"/>
-      <c r="C21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="1" t="s">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" t="s">
+        <v>369</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" t="s">
+        <v>370</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="1">
-        <v>2025</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22"/>
-      <c r="B22"/>
-      <c r="C22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K22" s="1" t="s">
+      <c r="F23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23"/>
-      <c r="B23"/>
-      <c r="C23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24"/>
-      <c r="B24"/>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" t="s">
+        <v>371</v>
+      </c>
       <c r="C24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>15</v>
@@ -2162,102 +3308,118 @@
       <c r="E24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="1">
-        <v>2025</v>
+      <c r="F24" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" t="s">
+        <v>372</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25"/>
-      <c r="B25"/>
-      <c r="C25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="1" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>222</v>
+      </c>
+      <c r="B26" t="s">
+        <v>373</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" s="1" t="s">
+      <c r="F26" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26"/>
-      <c r="B26"/>
-      <c r="C26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="1" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" t="s">
+        <v>374</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K26" s="1" t="s">
+      <c r="F27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28"/>
-      <c r="B28"/>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" t="s">
+        <v>375</v>
+      </c>
       <c r="C28" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>15</v>
@@ -2265,52 +3427,60 @@
       <c r="E28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="1">
-        <v>2025</v>
+      <c r="F28" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29"/>
-      <c r="B29"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" t="s">
+        <v>376</v>
+      </c>
       <c r="C29" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" s="1">
-        <v>2024</v>
+        <v>34</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30"/>
-      <c r="B30"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" t="s">
+        <v>377</v>
+      </c>
       <c r="C30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>15</v>
@@ -2319,23 +3489,27 @@
         <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31"/>
-      <c r="B31"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" t="s">
+        <v>378</v>
+      </c>
       <c r="C31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>15</v>
@@ -2343,24 +3517,28 @@
       <c r="E31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="1">
-        <v>2024</v>
+      <c r="F31" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>18</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32"/>
-      <c r="B32"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" t="s">
+        <v>379</v>
+      </c>
       <c r="C32" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>15</v>
@@ -2368,90 +3546,106 @@
       <c r="E32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="1">
-        <v>2023</v>
+      <c r="F32" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="K32" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" t="s">
+        <v>380</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33"/>
-      <c r="B33"/>
-      <c r="C33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="1" t="s">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" t="s">
+        <v>381</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" t="s">
+        <v>382</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F33" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34"/>
-      <c r="B34"/>
-      <c r="C34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K34" s="1" t="s">
+      <c r="F35" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A35"/>
-      <c r="B35"/>
-      <c r="C35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A36"/>
-      <c r="B36"/>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" t="s">
+        <v>383</v>
+      </c>
       <c r="C36" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>15</v>
@@ -2459,102 +3653,118 @@
       <c r="E36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F36" s="1">
-        <v>2024</v>
+      <c r="F36" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" t="s">
+        <v>384</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K37" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A37"/>
-      <c r="B37"/>
-      <c r="C37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="1" t="s">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" t="s">
+        <v>385</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F37" s="1">
-        <v>2024</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I37" s="1" t="s">
+      <c r="F38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K38" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38"/>
-      <c r="B38"/>
-      <c r="C38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" s="1" t="s">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" t="s">
+        <v>386</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F38" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K38" s="1" t="s">
+      <c r="F39" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A39"/>
-      <c r="B39"/>
-      <c r="C39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F39" s="1">
-        <v>2024</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40"/>
-      <c r="B40"/>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" t="s">
+        <v>387</v>
+      </c>
       <c r="C40" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>15</v>
@@ -2562,52 +3772,60 @@
       <c r="E40" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="1">
-        <v>2024</v>
+      <c r="F40" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A41"/>
-      <c r="B41"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" t="s">
+        <v>388</v>
+      </c>
       <c r="C41" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F41" s="1">
-        <v>2023</v>
+        <v>34</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42"/>
-      <c r="B42"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" t="s">
+        <v>389</v>
+      </c>
       <c r="C42" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>15</v>
@@ -2615,24 +3833,28 @@
       <c r="E42" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="1">
-        <v>2023</v>
+      <c r="F42" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43"/>
-      <c r="B43"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" t="s">
+        <v>390</v>
+      </c>
       <c r="C43" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>15</v>
@@ -2640,24 +3862,28 @@
       <c r="E43" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="1">
-        <v>2023</v>
+      <c r="F43" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>18</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A44"/>
-      <c r="B44"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" t="s">
+        <v>391</v>
+      </c>
       <c r="C44" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>15</v>
@@ -2665,90 +3891,106 @@
       <c r="E44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="1">
-        <v>2022</v>
+      <c r="F44" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="K44" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" t="s">
+        <v>392</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A45"/>
-      <c r="B45"/>
-      <c r="C45" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E45" s="1" t="s">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" t="s">
+        <v>393</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" t="s">
+        <v>394</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F45" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46"/>
-      <c r="B46"/>
-      <c r="C46" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F46" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K46" s="1" t="s">
+      <c r="F47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A47"/>
-      <c r="B47"/>
-      <c r="C47" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F47" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A48"/>
-      <c r="B48"/>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" t="s">
+        <v>395</v>
+      </c>
       <c r="C48" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>15</v>
@@ -2756,102 +3998,118 @@
       <c r="E48" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F48" s="1">
-        <v>2023</v>
+      <c r="F48" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" t="s">
+        <v>396</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="K49" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A49"/>
-      <c r="B49"/>
-      <c r="C49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="1" t="s">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" t="s">
+        <v>397</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F49" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I49" s="1" t="s">
+      <c r="F50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="K50" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A50"/>
-      <c r="B50"/>
-      <c r="C50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="1" t="s">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" t="s">
+        <v>398</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K50" s="1" t="s">
+      <c r="F51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A51"/>
-      <c r="B51"/>
-      <c r="C51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F51" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A52"/>
-      <c r="B52"/>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" t="s">
+        <v>399</v>
+      </c>
       <c r="C52" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>15</v>
@@ -2859,215 +4117,239 @@
       <c r="E52" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F52" s="1">
-        <v>2023</v>
+      <c r="F52" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L52" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>222</v>
+      </c>
+      <c r="B53" t="s">
+        <v>400</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L53" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A53"/>
-      <c r="B53"/>
-      <c r="C53" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F53" s="1" t="s">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>222</v>
+      </c>
+      <c r="B54" t="s">
+        <v>401</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="L53" s="1" t="s">
+      <c r="F54" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A54"/>
-      <c r="B54"/>
-      <c r="C54" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="G54" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A56"/>
-      <c r="B56"/>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>222</v>
+      </c>
+      <c r="B56" t="s">
+        <v>402</v>
+      </c>
       <c r="C56" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A57"/>
-      <c r="B57"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>222</v>
+      </c>
+      <c r="B57" t="s">
+        <v>403</v>
+      </c>
       <c r="C57" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A58"/>
       <c r="B58"/>
       <c r="C58" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>222</v>
+      </c>
+      <c r="B59" t="s">
+        <v>404</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A59"/>
-      <c r="B59"/>
-      <c r="C59" s="1" t="s">
+      <c r="L59" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>222</v>
+      </c>
+      <c r="B60" t="s">
+        <v>405</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A60"/>
-      <c r="B60"/>
-      <c r="C60" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="G60" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A61"/>
       <c r="B61"/>
       <c r="C61" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="G61" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="E1:E61" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -3075,21 +4357,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.54296875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.1796875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="23.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3109,17 +4391,21 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>407</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
@@ -3128,17 +4414,21 @@
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>408</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
@@ -3147,17 +4437,21 @@
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>409</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -3166,17 +4460,21 @@
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>410</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
@@ -3185,17 +4483,21 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>411</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
@@ -3204,81 +4506,81 @@
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9"/>
       <c r="B9"/>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.1796875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3298,14 +4600,18 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>412</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
@@ -3314,17 +4620,21 @@
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>413</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
@@ -3333,17 +4643,21 @@
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>414</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -3352,17 +4666,21 @@
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>415</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
@@ -3371,17 +4689,21 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>416</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
@@ -3390,31 +4712,31 @@
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.7265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3431,39 +4753,43 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>406</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3"/>
       <c r="B3"/>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/KatalonData/RADTestData/BeforePaymentsCorp.xlsx
+++ b/KatalonData/RADTestData/BeforePaymentsCorp.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{C62C7ED8-F369-4F4C-9058-5982C6F302E8}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F2D6D5-36F6-4272-96C8-6BD2062E6F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="3" windowHeight="15675" windowWidth="28996" xWindow="-98" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-98"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="6" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Estimated" r:id="rId1" sheetId="1"/>
-    <sheet name="Existing" r:id="rId2" sheetId="2"/>
-    <sheet name="Extension" r:id="rId3" sheetId="3"/>
-    <sheet name="NewTaxReturn" r:id="rId4" sheetId="4"/>
-    <sheet name="Personal_IND" r:id="rId5" sheetId="6"/>
-    <sheet name="Personal_JNT" r:id="rId6" sheetId="7"/>
-    <sheet name="Personal_EL" r:id="rId7" sheetId="8"/>
+    <sheet name="Estimated" sheetId="1" r:id="rId1"/>
+    <sheet name="Existing" sheetId="2" r:id="rId2"/>
+    <sheet name="Extension" sheetId="3" r:id="rId3"/>
+    <sheet name="NewTaxReturn" sheetId="4" r:id="rId4"/>
+    <sheet name="Personal_IND" sheetId="6" r:id="rId5"/>
+    <sheet name="Personal_JNT" sheetId="7" r:id="rId6"/>
+    <sheet name="Personal_EL" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">NewTaxReturn!$E$1:$E$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NewTaxReturn!$E$1:$E$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="216">
   <si>
     <t>Result</t>
   </si>
@@ -395,914 +395,310 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Sat May 23 12:59:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 12:59:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:00:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:00:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:01:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:02:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:02:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:03:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:03:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:04:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:04:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:05:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:05:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:06:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:06:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:07:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:08:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:08:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:09:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:09:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:10:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:10:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:11:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:11:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:12:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:12:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:13:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:13:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:14:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:14:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:15:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:15:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:16:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:16:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:17:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:17:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:18:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:19:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:19:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:20:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:20:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:21:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:21:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:22:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:22:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:23:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:23:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:24:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:24:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:25:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:25:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:26:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:26:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:27:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:27:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:28:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:28:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:29:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:30:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:30:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:31:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:31:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:32:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:32:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:33:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:33:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:34:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:35:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:35:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:36:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:36:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:37:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:37:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:38:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:38:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:39:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:40:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:40:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:41:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:41:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:42:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:42:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:43:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:43:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:44:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:44:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:45:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 13:45:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 14:36:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 14:36:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 14:37:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 14:37:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 14:38:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 14:39:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 14:39:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 14:40:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 14:40:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 14:41:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 14:41:51 EDT 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Fri May 29 12:36:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:37:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:38:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:39:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:39:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:40:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:40:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:42:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:42:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:43:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:43:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:44:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:44:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:45:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:46:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:46:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:47:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:47:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:48:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:48:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:49:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:49:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:50:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:50:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:51:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:52:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:53:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:54:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:54:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:55:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:55:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:56:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:57:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:57:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:58:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:58:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:59:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 12:59:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:00:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:00:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:01:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:01:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:02:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:03:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:03:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:04:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:04:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:05:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:05:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:06:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:06:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:07:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:08:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:08:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:09:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:10:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:10:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:11:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:12:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:12:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:13:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:13:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:14:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:14:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:15:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:15:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:16:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:16:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:17:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:18:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:18:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:19:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:19:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:20:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:21:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:23:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:24:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:25:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:26:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:27:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:28:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:30:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:31:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:32:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:33:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:35:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:37:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:38:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:40:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:42:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:43:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:44:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:46:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:47:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:48:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:49:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:50:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:51:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:53:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 13:54:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:22:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:23:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:25:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:26:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:27:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:28:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:29:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:31:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:32:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:33:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:35:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:36:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:37:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:38:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:39:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:40:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:42:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:43:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:44:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:45:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:46:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:47:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:48:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:50:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:51:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:52:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:54:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:55:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:56:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:58:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:59:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:00:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:01:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:03:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:04:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:05:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:06:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:07:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:08:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:10:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:11:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:13:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:14:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:15:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:16:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:17:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:19:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:20:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:21:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:22:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:23:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:24:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:26:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:27:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:28:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:29:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:30:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:32:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:33:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:35:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:36:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:37:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:38:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:39:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:40:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:41:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:43:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:44:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:45:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:46:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:47:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:49:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:50:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:51:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:52:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:53:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:54:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:55:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:57:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:58:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 00:59:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:00:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:01:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:02:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:04:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:06:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:07:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:09:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:11:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:12:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:14:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:15:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:16:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:17:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:18:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:20:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:21:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:22:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:23:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:25:11 EDT 2026</t>
+    <t>Fri Jun 05 21:21:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:23:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:24:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:25:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:27:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:28:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:29:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:31:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:32:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:34:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:35:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:36:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:38:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:39:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:40:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:41:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:43:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:44:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:45:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:47:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:48:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:49:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:50:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:52:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:53:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:54:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:55:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:57:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:59:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:00:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:02:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:03:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:04:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:05:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:07:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:08:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:10:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:11:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:12:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:14:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:15:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:16:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:18:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:19:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:21:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:22:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:23:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:25:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:26:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:27:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:30:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:31:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:32:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:34:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:35:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:36:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:38:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:39:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:40:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:41:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:43:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:44:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:45:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:47:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:48:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:49:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:51:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:52:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:54:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:55:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:56:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:58:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:59:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:00:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:02:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:03:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:04:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:06:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:07:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:08:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:10:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:11:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:12:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:14:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:15:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:16:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:18:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:19:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:20:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:22:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:23:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:25:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:27:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:28:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:30:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:31:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:32:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:33:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:35:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 11:36:00 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1351,19 +747,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1380,10 +776,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1418,7 +814,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1470,7 +866,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1581,21 +977,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1612,7 +1008,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1664,28 +1060,28 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
-  <dimension ref="A1:K8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1725,7 +1121,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>116</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1754,7 +1150,7 @@
         <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>318</v>
+        <v>117</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1783,7 +1179,7 @@
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>319</v>
+        <v>118</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1815,7 +1211,7 @@
         <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>320</v>
+        <v>119</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1847,7 +1243,7 @@
         <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>321</v>
+        <v>120</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1879,7 +1275,7 @@
         <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>322</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1908,10 +1304,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>323</v>
+        <v>122</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1931,8 +1327,8 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1940,20 +1336,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
-  <dimension ref="A1:K21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1993,7 +1389,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>123</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2016,7 +1412,7 @@
         <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>325</v>
+        <v>124</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2039,7 +1435,7 @@
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>326</v>
+        <v>125</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2062,7 +1458,7 @@
         <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>327</v>
+        <v>126</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2088,7 +1484,7 @@
         <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>328</v>
+        <v>127</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2114,7 +1510,7 @@
         <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>329</v>
+        <v>128</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2137,7 +1533,7 @@
         <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>330</v>
+        <v>129</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2160,7 +1556,7 @@
         <v>115</v>
       </c>
       <c r="B9" t="s">
-        <v>331</v>
+        <v>130</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2183,7 +1579,7 @@
         <v>115</v>
       </c>
       <c r="B10" t="s">
-        <v>332</v>
+        <v>131</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2206,7 +1602,7 @@
         <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>333</v>
+        <v>132</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2229,7 +1625,7 @@
         <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>334</v>
+        <v>133</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2252,7 +1648,7 @@
         <v>115</v>
       </c>
       <c r="B13" t="s">
-        <v>335</v>
+        <v>134</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2275,7 +1671,7 @@
         <v>115</v>
       </c>
       <c r="B14" t="s">
-        <v>336</v>
+        <v>135</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2298,7 +1694,7 @@
         <v>115</v>
       </c>
       <c r="B15" t="s">
-        <v>337</v>
+        <v>136</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2318,7 +1714,7 @@
         <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>338</v>
+        <v>137</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2344,7 +1740,7 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>339</v>
+        <v>138</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2367,7 +1763,7 @@
         <v>115</v>
       </c>
       <c r="B18" t="s">
-        <v>340</v>
+        <v>139</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2406,10 +1802,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="B20" t="s">
-        <v>341</v>
+        <v>140</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2426,10 +1822,10 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>342</v>
+        <v>141</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -2448,7 +1844,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -2456,19 +1852,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
-  <dimension ref="A1:J7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -2505,7 +1901,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>343</v>
+        <v>142</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2531,7 +1927,7 @@
         <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>344</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2554,7 +1950,7 @@
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>345</v>
+        <v>144</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2580,7 +1976,7 @@
         <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>346</v>
+        <v>145</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2606,7 +2002,7 @@
         <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>347</v>
+        <v>146</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2632,7 +2028,7 @@
         <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>348</v>
+        <v>147</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2655,7 +2051,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -2663,20 +2059,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
-  <dimension ref="A1:M61"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
+  <dimension ref="A1:L61"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
-    <col min="11" max="11" style="1" width="9.19921875" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
-    <col min="13" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.19921875" style="1" collapsed="1"/>
+    <col min="12" max="12" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
@@ -2722,7 +2118,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>349</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2745,7 +2141,7 @@
         <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>350</v>
+        <v>149</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2771,7 +2167,7 @@
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>351</v>
+        <v>150</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2797,7 +2193,7 @@
         <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>352</v>
+        <v>151</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2823,7 +2219,7 @@
         <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>353</v>
+        <v>152</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2849,7 +2245,7 @@
         <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>354</v>
+        <v>153</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2872,7 +2268,7 @@
         <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>355</v>
+        <v>154</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2895,10 +2291,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
-        <v>356</v>
+        <v>155</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2924,7 +2320,7 @@
         <v>115</v>
       </c>
       <c r="B10" t="s">
-        <v>357</v>
+        <v>156</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2950,7 +2346,7 @@
         <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>358</v>
+        <v>157</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2976,7 +2372,7 @@
         <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>359</v>
+        <v>158</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2999,7 +2395,7 @@
         <v>115</v>
       </c>
       <c r="B13" t="s">
-        <v>360</v>
+        <v>159</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -3025,7 +2421,7 @@
         <v>115</v>
       </c>
       <c r="B14" t="s">
-        <v>361</v>
+        <v>160</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -3051,7 +2447,7 @@
         <v>115</v>
       </c>
       <c r="B15" t="s">
-        <v>362</v>
+        <v>161</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -3077,7 +2473,7 @@
         <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>363</v>
+        <v>162</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -3103,7 +2499,7 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>364</v>
+        <v>163</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -3132,7 +2528,7 @@
         <v>115</v>
       </c>
       <c r="B18" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -3161,7 +2557,7 @@
         <v>115</v>
       </c>
       <c r="B19" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -3190,7 +2586,7 @@
         <v>115</v>
       </c>
       <c r="B20" t="s">
-        <v>367</v>
+        <v>215</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -3213,7 +2609,7 @@
         <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>368</v>
+        <v>166</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -3242,7 +2638,7 @@
         <v>115</v>
       </c>
       <c r="B22" t="s">
-        <v>369</v>
+        <v>167</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -3271,7 +2667,7 @@
         <v>115</v>
       </c>
       <c r="B23" t="s">
-        <v>370</v>
+        <v>168</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -3297,7 +2693,7 @@
         <v>115</v>
       </c>
       <c r="B24" t="s">
-        <v>371</v>
+        <v>169</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -3326,7 +2722,7 @@
         <v>115</v>
       </c>
       <c r="B25" t="s">
-        <v>372</v>
+        <v>170</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -3355,10 +2751,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="B26" t="s">
-        <v>373</v>
+        <v>171</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -3387,7 +2783,7 @@
         <v>115</v>
       </c>
       <c r="B27" t="s">
-        <v>374</v>
+        <v>172</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
@@ -3416,7 +2812,7 @@
         <v>115</v>
       </c>
       <c r="B28" t="s">
-        <v>375</v>
+        <v>173</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -3448,7 +2844,7 @@
         <v>115</v>
       </c>
       <c r="B29" t="s">
-        <v>376</v>
+        <v>174</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -3477,7 +2873,7 @@
         <v>115</v>
       </c>
       <c r="B30" t="s">
-        <v>377</v>
+        <v>175</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
@@ -3506,7 +2902,7 @@
         <v>115</v>
       </c>
       <c r="B31" t="s">
-        <v>378</v>
+        <v>176</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
@@ -3535,7 +2931,7 @@
         <v>115</v>
       </c>
       <c r="B32" t="s">
-        <v>379</v>
+        <v>177</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -3558,7 +2954,7 @@
         <v>115</v>
       </c>
       <c r="B33" t="s">
-        <v>380</v>
+        <v>178</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -3587,7 +2983,7 @@
         <v>115</v>
       </c>
       <c r="B34" t="s">
-        <v>381</v>
+        <v>179</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
@@ -3616,7 +3012,7 @@
         <v>115</v>
       </c>
       <c r="B35" t="s">
-        <v>382</v>
+        <v>180</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
@@ -3642,7 +3038,7 @@
         <v>115</v>
       </c>
       <c r="B36" t="s">
-        <v>383</v>
+        <v>181</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -3671,7 +3067,7 @@
         <v>115</v>
       </c>
       <c r="B37" t="s">
-        <v>384</v>
+        <v>182</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
@@ -3703,7 +3099,7 @@
         <v>115</v>
       </c>
       <c r="B38" t="s">
-        <v>385</v>
+        <v>183</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -3732,7 +3128,7 @@
         <v>115</v>
       </c>
       <c r="B39" t="s">
-        <v>386</v>
+        <v>184</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
@@ -3761,7 +3157,7 @@
         <v>115</v>
       </c>
       <c r="B40" t="s">
-        <v>387</v>
+        <v>185</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -3793,7 +3189,7 @@
         <v>115</v>
       </c>
       <c r="B41" t="s">
-        <v>388</v>
+        <v>186</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -3822,7 +3218,7 @@
         <v>115</v>
       </c>
       <c r="B42" t="s">
-        <v>389</v>
+        <v>187</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -3851,7 +3247,7 @@
         <v>115</v>
       </c>
       <c r="B43" t="s">
-        <v>390</v>
+        <v>188</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -3880,7 +3276,7 @@
         <v>115</v>
       </c>
       <c r="B44" t="s">
-        <v>391</v>
+        <v>189</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
@@ -3903,7 +3299,7 @@
         <v>115</v>
       </c>
       <c r="B45" t="s">
-        <v>392</v>
+        <v>190</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -3932,7 +3328,7 @@
         <v>115</v>
       </c>
       <c r="B46" t="s">
-        <v>393</v>
+        <v>191</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3961,7 +3357,7 @@
         <v>115</v>
       </c>
       <c r="B47" t="s">
-        <v>394</v>
+        <v>192</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3987,7 +3383,7 @@
         <v>115</v>
       </c>
       <c r="B48" t="s">
-        <v>395</v>
+        <v>193</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -4016,7 +3412,7 @@
         <v>115</v>
       </c>
       <c r="B49" t="s">
-        <v>396</v>
+        <v>194</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -4048,7 +3444,7 @@
         <v>115</v>
       </c>
       <c r="B50" t="s">
-        <v>397</v>
+        <v>195</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>29</v>
@@ -4077,7 +3473,7 @@
         <v>115</v>
       </c>
       <c r="B51" t="s">
-        <v>398</v>
+        <v>196</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>29</v>
@@ -4106,7 +3502,7 @@
         <v>115</v>
       </c>
       <c r="B52" t="s">
-        <v>399</v>
+        <v>197</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>29</v>
@@ -4135,10 +3531,10 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="B53" t="s">
-        <v>400</v>
+        <v>198</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>29</v>
@@ -4158,10 +3554,10 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="B54" t="s">
-        <v>401</v>
+        <v>199</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>29</v>
@@ -4206,10 +3602,10 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="B56" t="s">
-        <v>402</v>
+        <v>200</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
@@ -4229,10 +3625,10 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="B57" t="s">
-        <v>403</v>
+        <v>201</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>29</v>
@@ -4277,10 +3673,10 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="B59" t="s">
-        <v>404</v>
+        <v>202</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
@@ -4300,10 +3696,10 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="B60" t="s">
-        <v>405</v>
+        <v>203</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>29</v>
@@ -4349,7 +3745,7 @@
   </sheetData>
   <autoFilter ref="E1:E61" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -4357,18 +3753,18 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
-  <dimension ref="A1:I9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -4402,7 +3798,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>407</v>
+        <v>205</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4425,7 +3821,7 @@
         <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>408</v>
+        <v>206</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4448,7 +3844,7 @@
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>409</v>
+        <v>207</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4471,7 +3867,7 @@
         <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>410</v>
+        <v>208</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4494,7 +3890,7 @@
         <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>411</v>
+        <v>209</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4561,23 +3957,23 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
-  <dimension ref="A1:H6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
-    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4608,7 +4004,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>412</v>
+        <v>210</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4631,7 +4027,7 @@
         <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>413</v>
+        <v>211</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4654,7 +4050,7 @@
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>414</v>
+        <v>212</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4677,7 +4073,7 @@
         <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>415</v>
+        <v>213</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4700,7 +4096,7 @@
         <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>416</v>
+        <v>214</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4719,21 +4115,21 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4761,7 +4157,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>406</v>
+        <v>204</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4790,6 +4186,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KatalonData/RADTestData/BeforePaymentsCorp.xlsx
+++ b/KatalonData/RADTestData/BeforePaymentsCorp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F2D6D5-36F6-4272-96C8-6BD2062E6F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0AAA07F-0506-4BF8-9522-5F6C3162805A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="6" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="327">
   <si>
     <t>Result</t>
   </si>
@@ -395,9 +395,6 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Fri Jun 05 21:21:51 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri Jun 05 21:23:10 EDT 2026</t>
   </si>
   <si>
@@ -470,9 +467,6 @@
     <t>Fri Jun 05 21:53:20 EDT 2026</t>
   </si>
   <si>
-    <t>Fri Jun 05 21:54:37 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri Jun 05 21:55:51 EDT 2026</t>
   </si>
   <si>
@@ -617,9 +611,6 @@
     <t>Fri Jun 05 23:00:48 EDT 2026</t>
   </si>
   <si>
-    <t>Fri Jun 05 23:02:03 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri Jun 05 23:03:31 EDT 2026</t>
   </si>
   <si>
@@ -647,9 +638,6 @@
     <t>Fri Jun 05 23:14:10 EDT 2026</t>
   </si>
   <si>
-    <t>Fri Jun 05 23:15:23 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri Jun 05 23:16:47 EDT 2026</t>
   </si>
   <si>
@@ -693,12 +681,358 @@
   </si>
   <si>
     <t>Sat Jun 06 11:36:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:21:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>MFInsNum</t>
+  </si>
+  <si>
+    <t>Motor Fuel Floor Tax</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:38:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:39:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:40:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:40:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:41:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:31:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:32:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:32:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:33:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:34:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:34:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:35:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:36:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:36:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:37:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:38:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:38:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:39:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:40:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:40:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:41:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:42:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:42:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:43:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:43:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:44:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:45:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:45:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:46:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:46:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:47:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:48:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:48:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:49:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:49:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:50:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:51:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:51:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:52:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:52:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:53:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:54:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:54:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:55:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:55:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:56:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:57:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:57:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:58:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:58:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:59:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:00:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:00:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:01:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:01:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:02:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:03:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:03:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:04:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:04:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:05:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:06:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:06:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:07:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:08:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:08:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:09:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:09:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:10:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:11:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:11:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:12:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:12:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:13:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:14:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:14:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:15:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:15:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:16:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:17:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:17:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:18:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:18:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:19:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:20:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:20:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:21:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:21:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:22:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:23:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:23:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:24:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:24:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:25:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:26:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:26:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:27:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:27:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:28:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:29:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:29:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:30:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:31:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:31:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:32:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:32:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:33:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:34:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:34:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:35:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:36:03 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1071,17 +1405,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1117,11 +1451,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>116</v>
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1146,11 +1480,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>117</v>
+      <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1175,11 +1509,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" t="s">
-        <v>118</v>
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1207,11 +1541,11 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>119</v>
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1239,11 +1573,11 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>120</v>
+      <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1271,11 +1605,11 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" t="s">
-        <v>121</v>
+      <c r="A7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1303,11 +1637,11 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B8" t="s">
-        <v>122</v>
+      <c r="A8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1340,16 +1674,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1385,11 +1719,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>123</v>
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1408,11 +1742,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>124</v>
+      <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1431,11 +1765,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" t="s">
-        <v>125</v>
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1454,11 +1788,11 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>126</v>
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1480,11 +1814,11 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>127</v>
+      <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1506,11 +1840,11 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" t="s">
-        <v>128</v>
+      <c r="A7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1529,11 +1863,11 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B8" t="s">
-        <v>129</v>
+      <c r="A8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1552,11 +1886,11 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" t="s">
-        <v>130</v>
+      <c r="A9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -1575,11 +1909,11 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" t="s">
-        <v>131</v>
+      <c r="A10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -1598,11 +1932,11 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B11" t="s">
-        <v>132</v>
+      <c r="A11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -1621,11 +1955,11 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" t="s">
-        <v>133</v>
+      <c r="A12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -1644,11 +1978,11 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" t="s">
-        <v>134</v>
+      <c r="A13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -1667,11 +2001,11 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" t="s">
-        <v>135</v>
+      <c r="A14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -1690,11 +2024,11 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" t="s">
-        <v>136</v>
+      <c r="A15" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -1710,11 +2044,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" t="s">
-        <v>137</v>
+      <c r="A16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -1736,11 +2070,11 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" t="s">
-        <v>138</v>
+      <c r="A17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -1759,11 +2093,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" t="s">
-        <v>139</v>
+      <c r="A18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -1782,8 +2116,6 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19"/>
-      <c r="B19"/>
       <c r="C19" s="1" t="s">
         <v>32</v>
       </c>
@@ -1801,11 +2133,11 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>115</v>
-      </c>
-      <c r="B20" t="s">
-        <v>140</v>
+      <c r="A20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -1821,14 +2153,8 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" t="s">
-        <v>141</v>
-      </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>107</v>
@@ -1856,15 +2182,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1897,11 +2223,11 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>142</v>
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1923,11 +2249,11 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>143</v>
+      <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1946,11 +2272,11 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" t="s">
-        <v>144</v>
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1972,11 +2298,11 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>145</v>
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1998,11 +2324,11 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>146</v>
+      <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2024,11 +2350,11 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" t="s">
-        <v>147</v>
+      <c r="A7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2060,22 +2386,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.19921875" style="1" collapsed="1"/>
-    <col min="12" max="12" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
+    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
+    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2107,18 +2434,21 @@
         <v>108</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>148</v>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>259</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2132,16 +2462,16 @@
       <c r="F2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>149</v>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2158,16 +2488,16 @@
       <c r="G3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" t="s">
-        <v>150</v>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2184,16 +2514,16 @@
       <c r="G4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>151</v>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>262</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2210,16 +2540,16 @@
       <c r="G5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>152</v>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>263</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2236,16 +2566,16 @@
       <c r="G6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" t="s">
-        <v>153</v>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2259,16 +2589,16 @@
       <c r="F7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B8" t="s">
-        <v>154</v>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>265</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2285,16 +2615,16 @@
       <c r="G8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" t="s">
-        <v>155</v>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>266</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2311,16 +2641,16 @@
       <c r="G9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" t="s">
-        <v>156</v>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>267</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2337,16 +2667,16 @@
       <c r="G10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B11" t="s">
-        <v>157</v>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2363,16 +2693,16 @@
       <c r="G11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" t="s">
-        <v>158</v>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2386,16 +2716,16 @@
       <c r="F12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" t="s">
-        <v>159</v>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2412,16 +2742,16 @@
       <c r="G13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" t="s">
-        <v>160</v>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2438,16 +2768,16 @@
       <c r="G14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" t="s">
-        <v>161</v>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>272</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2464,16 +2794,16 @@
       <c r="G15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" t="s">
-        <v>162</v>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>273</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2490,16 +2820,16 @@
       <c r="G16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" t="s">
-        <v>163</v>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2519,16 +2849,16 @@
       <c r="I17" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" t="s">
-        <v>164</v>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2548,16 +2878,16 @@
       <c r="I18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B19" t="s">
-        <v>165</v>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -2577,16 +2907,16 @@
       <c r="I19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>115</v>
-      </c>
-      <c r="B20" t="s">
-        <v>215</v>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>277</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2600,16 +2930,16 @@
       <c r="F20" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" t="s">
-        <v>166</v>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -2629,16 +2959,16 @@
       <c r="J21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" t="s">
-        <v>167</v>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -2658,16 +2988,16 @@
       <c r="I22" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>115</v>
-      </c>
-      <c r="B23" t="s">
-        <v>168</v>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -2684,16 +3014,16 @@
       <c r="H23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>115</v>
-      </c>
-      <c r="B24" t="s">
-        <v>169</v>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -2713,16 +3043,16 @@
       <c r="I24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>115</v>
-      </c>
-      <c r="B25" t="s">
-        <v>170</v>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -2745,16 +3075,16 @@
       <c r="I25" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="L25" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>115</v>
-      </c>
-      <c r="B26" t="s">
-        <v>171</v>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>283</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -2774,16 +3104,16 @@
       <c r="I26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>115</v>
-      </c>
-      <c r="B27" t="s">
-        <v>172</v>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
@@ -2803,16 +3133,16 @@
       <c r="H27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>115</v>
-      </c>
-      <c r="B28" t="s">
-        <v>173</v>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -2832,19 +3162,19 @@
       <c r="I28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>115</v>
-      </c>
-      <c r="B29" t="s">
-        <v>174</v>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -2864,16 +3194,16 @@
       <c r="I29" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="L29" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" t="s">
-        <v>175</v>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>287</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
@@ -2893,16 +3223,16 @@
       <c r="I30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>115</v>
-      </c>
-      <c r="B31" t="s">
-        <v>176</v>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
@@ -2922,16 +3252,16 @@
       <c r="I31" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="L31" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>115</v>
-      </c>
-      <c r="B32" t="s">
-        <v>177</v>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>289</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -2945,16 +3275,16 @@
       <c r="F32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" t="s">
-        <v>178</v>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -2974,16 +3304,16 @@
       <c r="J33" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>115</v>
-      </c>
-      <c r="B34" t="s">
-        <v>179</v>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
@@ -3003,16 +3333,16 @@
       <c r="I34" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="L34" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>115</v>
-      </c>
-      <c r="B35" t="s">
-        <v>180</v>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
@@ -3029,16 +3359,16 @@
       <c r="H35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="L35" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>115</v>
-      </c>
-      <c r="B36" t="s">
-        <v>181</v>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -3058,16 +3388,16 @@
       <c r="I36" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>115</v>
-      </c>
-      <c r="B37" t="s">
-        <v>182</v>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
@@ -3090,16 +3420,16 @@
       <c r="I37" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>115</v>
-      </c>
-      <c r="B38" t="s">
-        <v>183</v>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -3119,16 +3449,16 @@
       <c r="I38" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" t="s">
-        <v>184</v>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>296</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
@@ -3148,16 +3478,16 @@
       <c r="H39" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="L39" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>115</v>
-      </c>
-      <c r="B40" t="s">
-        <v>185</v>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -3177,19 +3507,19 @@
       <c r="I40" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="L40" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="M40" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>115</v>
-      </c>
-      <c r="B41" t="s">
-        <v>186</v>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -3209,16 +3539,16 @@
       <c r="I41" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>115</v>
-      </c>
-      <c r="B42" t="s">
-        <v>187</v>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -3238,16 +3568,16 @@
       <c r="I42" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="L42" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>115</v>
-      </c>
-      <c r="B43" t="s">
-        <v>188</v>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -3267,16 +3597,16 @@
       <c r="I43" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="L43" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>115</v>
-      </c>
-      <c r="B44" t="s">
-        <v>189</v>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>301</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
@@ -3290,16 +3620,16 @@
       <c r="F44" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>115</v>
-      </c>
-      <c r="B45" t="s">
-        <v>190</v>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -3319,16 +3649,16 @@
       <c r="J45" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>115</v>
-      </c>
-      <c r="B46" t="s">
-        <v>191</v>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3348,16 +3678,16 @@
       <c r="I46" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>115</v>
-      </c>
-      <c r="B47" t="s">
-        <v>192</v>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3374,16 +3704,16 @@
       <c r="H47" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>115</v>
-      </c>
-      <c r="B48" t="s">
-        <v>193</v>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A48" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -3403,16 +3733,16 @@
       <c r="I48" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>115</v>
-      </c>
-      <c r="B49" t="s">
-        <v>194</v>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -3435,16 +3765,16 @@
       <c r="I49" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="L49" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>115</v>
-      </c>
-      <c r="B50" t="s">
-        <v>195</v>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A50" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>29</v>
@@ -3464,16 +3794,16 @@
       <c r="I50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>115</v>
-      </c>
-      <c r="B51" t="s">
-        <v>196</v>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A51" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>308</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>29</v>
@@ -3493,16 +3823,16 @@
       <c r="H51" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="L51" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>115</v>
-      </c>
-      <c r="B52" t="s">
-        <v>197</v>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>29</v>
@@ -3522,19 +3852,19 @@
       <c r="I52" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="L52" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L52" s="1" t="s">
+      <c r="M52" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>115</v>
-      </c>
-      <c r="B53" t="s">
-        <v>198</v>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>29</v>
@@ -3548,19 +3878,16 @@
       <c r="F53" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L53" s="1" t="s">
+      <c r="M53" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>115</v>
-      </c>
-      <c r="B54" t="s">
-        <v>199</v>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="B54" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>15</v>
@@ -3574,13 +3901,11 @@
       <c r="G54" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L54" s="1" t="s">
+      <c r="M54" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A55"/>
-      <c r="B55"/>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C55" s="1" t="s">
         <v>32</v>
       </c>
@@ -3600,12 +3925,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>115</v>
-      </c>
-      <c r="B56" t="s">
-        <v>200</v>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A56" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
@@ -3619,19 +3944,16 @@
       <c r="F56" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L56" s="1" t="s">
+      <c r="M56" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>115</v>
-      </c>
-      <c r="B57" t="s">
-        <v>201</v>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="B57" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>15</v>
@@ -3645,13 +3967,11 @@
       <c r="G57" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L57" s="1" t="s">
+      <c r="M57" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A58"/>
-      <c r="B58"/>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C58" s="1" t="s">
         <v>32</v>
       </c>
@@ -3671,12 +3991,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
-        <v>115</v>
-      </c>
-      <c r="B59" t="s">
-        <v>202</v>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A59" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
@@ -3690,19 +4010,16 @@
       <c r="F59" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L59" s="1" t="s">
+      <c r="M59" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
-        <v>115</v>
-      </c>
-      <c r="B60" t="s">
-        <v>203</v>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="B60" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>15</v>
@@ -3716,13 +4033,11 @@
       <c r="G60" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L60" s="1" t="s">
+      <c r="M60" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A61"/>
-      <c r="B61"/>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C61" s="1" t="s">
         <v>32</v>
       </c>
@@ -3740,6 +4055,84 @@
       </c>
       <c r="I61" s="1" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A62" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A63" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A64" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B64" t="s" s="1">
+        <v>315</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3757,14 +4150,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -3794,11 +4187,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>205</v>
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -3817,11 +4210,11 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>206</v>
+      <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>318</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -3840,11 +4233,11 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" t="s">
-        <v>207</v>
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>319</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -3863,11 +4256,11 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>208</v>
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -3886,11 +4279,11 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>209</v>
+      <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -3909,8 +4302,6 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7"/>
-      <c r="B7"/>
       <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
@@ -3925,8 +4316,6 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8"/>
-      <c r="B8"/>
       <c r="C8" s="1" t="s">
         <v>32</v>
       </c>
@@ -3941,8 +4330,6 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9"/>
-      <c r="B9"/>
       <c r="C9" s="1" t="s">
         <v>32</v>
       </c>
@@ -3966,14 +4353,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4000,11 +4387,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>210</v>
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4023,11 +4410,11 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>211</v>
+      <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>323</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4046,11 +4433,11 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" t="s">
-        <v>212</v>
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4069,11 +4456,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>213</v>
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4092,11 +4479,11 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>214</v>
+      <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4124,12 +4511,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4153,11 +4540,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>204</v>
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4173,8 +4560,6 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3"/>
-      <c r="B3"/>
       <c r="C3" s="1" t="s">
         <v>32</v>
       </c>

--- a/KatalonData/RADTestData/BeforePaymentsCorp.xlsx
+++ b/KatalonData/RADTestData/BeforePaymentsCorp.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0AAA07F-0506-4BF8-9522-5F6C3162805A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E327BBC7-BD82-4D75-B281-88300BEF06DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="3075" yWindow="3405" windowWidth="21600" windowHeight="11325" activeTab="4" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="224">
   <si>
     <t>Result</t>
   </si>
@@ -395,644 +395,334 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Fri Jun 05 21:23:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:24:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:25:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:27:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:28:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:29:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:31:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:32:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:34:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:35:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:36:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:38:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:39:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:40:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:41:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:43:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:44:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:45:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:47:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:48:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:49:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:50:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:52:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:53:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:55:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:57:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:59:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:00:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:02:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:03:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:04:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:05:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:07:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:08:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:10:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:11:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:12:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:14:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:15:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:16:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:18:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:19:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:21:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:22:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:23:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:25:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:26:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:27:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:30:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:31:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:32:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:34:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:35:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:36:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:38:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:39:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:40:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:41:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:43:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:44:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:45:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:47:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:48:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:49:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:51:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:52:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:54:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:55:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:56:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:58:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:59:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:00:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:03:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:04:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:06:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:07:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:08:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:10:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:11:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:12:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:14:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:16:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:18:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:19:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:20:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:22:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:23:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:25:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:27:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:28:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:30:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:31:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:32:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:33:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:35:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 11:36:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:21:59 EDT 2026</t>
-  </si>
-  <si>
     <t>MFInsNum</t>
   </si>
   <si>
     <t>Motor Fuel Floor Tax</t>
   </si>
   <si>
-    <t>Fri Jul 10 15:38:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 15:39:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 15:40:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 15:40:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 15:41:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:31:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:32:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:32:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:33:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:34:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:34:57 EDT 2026</t>
+    <t>Sat Jul 11 23:36:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:36:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:37:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:38:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:38:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:39:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:40:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:40:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:41:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:42:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:42:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:43:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:43:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:44:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:45:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:45:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:46:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:46:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:47:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:48:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:48:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:49:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:49:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:50:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:51:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:51:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:52:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:52:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:53:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:54:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:54:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:55:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:55:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:56:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:57:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:57:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:58:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:58:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 11 23:59:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:00:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:00:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:01:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:01:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:02:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:03:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:03:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:04:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:04:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:05:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:06:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:06:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:07:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:08:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:08:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:09:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:09:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:10:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:11:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:11:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:12:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:12:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:13:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:14:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:14:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:15:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:15:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:16:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:17:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:17:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:18:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:18:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:19:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:20:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:20:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:21:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:21:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:22:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:23:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:23:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:24:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:24:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:25:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:26:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:26:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:27:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:27:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:28:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:29:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:29:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:30:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:31:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:31:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:32:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:32:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:33:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:34:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:34:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:35:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:36:03 EDT 2026</t>
   </si>
   <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Sat Jul 11 23:35:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:36:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:36:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:37:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:38:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:38:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:39:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:40:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:40:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:41:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:42:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:42:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:43:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:43:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:44:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:45:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:45:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:46:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:46:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:47:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:48:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:48:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:49:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:49:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:50:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:51:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:51:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:52:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:52:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:53:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:54:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:54:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:55:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:55:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:56:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:57:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:57:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:58:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:58:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 11 23:59:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:00:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:00:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:01:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:01:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:02:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:03:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:03:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:04:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:04:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:05:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:06:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:06:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:07:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:08:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:08:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:09:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:09:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:10:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:11:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:11:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:12:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:12:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:13:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:14:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:14:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:15:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:15:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:16:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:17:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:17:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:18:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:18:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:19:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:20:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:20:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:21:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:21:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:22:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:23:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:23:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:24:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:24:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:25:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:26:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:26:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:27:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:27:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:28:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:29:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:29:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:30:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:31:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:31:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:32:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:32:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:33:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:34:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:34:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:35:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:36:03 EDT 2026</t>
+    <t>Sun Aug 02 14:28:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 14:30:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 14:31:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:33:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:34:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:36:16 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1405,17 +1095,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1455,7 +1145,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>228</v>
+        <v>118</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1484,7 +1174,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1513,7 +1203,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1545,7 +1235,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>231</v>
+        <v>121</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1577,7 +1267,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>232</v>
+        <v>122</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1609,7 +1299,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>233</v>
+        <v>123</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1641,7 +1331,7 @@
         <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>234</v>
+        <v>124</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1674,16 +1364,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1723,7 +1413,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>235</v>
+        <v>125</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1746,7 +1436,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>236</v>
+        <v>126</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1769,7 +1459,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1792,7 +1482,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1818,7 +1508,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>239</v>
+        <v>129</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1844,7 +1534,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1867,7 +1557,7 @@
         <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>241</v>
+        <v>131</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1890,7 +1580,7 @@
         <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>242</v>
+        <v>132</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -1913,7 +1603,7 @@
         <v>115</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>243</v>
+        <v>133</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -1936,7 +1626,7 @@
         <v>115</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -1959,7 +1649,7 @@
         <v>115</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -1982,7 +1672,7 @@
         <v>115</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>246</v>
+        <v>136</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2005,7 +1695,7 @@
         <v>115</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>247</v>
+        <v>137</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2028,7 +1718,7 @@
         <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>248</v>
+        <v>138</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2048,7 +1738,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>249</v>
+        <v>139</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2074,7 +1764,7 @@
         <v>115</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2097,7 +1787,7 @@
         <v>115</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>251</v>
+        <v>141</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2137,7 +1827,7 @@
         <v>115</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>252</v>
+        <v>142</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2182,15 +1872,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -2227,7 +1917,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>253</v>
+        <v>143</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2253,7 +1943,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>254</v>
+        <v>144</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2276,7 +1966,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>255</v>
+        <v>145</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2302,7 +1992,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>256</v>
+        <v>146</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2328,7 +2018,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>257</v>
+        <v>147</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2354,7 +2044,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>258</v>
+        <v>148</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2389,17 +2079,17 @@
   <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
-    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
-    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="19.796875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.19921875" style="1" collapsed="1"/>
+    <col min="13" max="13" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -2434,7 +2124,7 @@
         <v>108</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>213</v>
+        <v>116</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>43</v>
@@ -2448,7 +2138,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>259</v>
+        <v>149</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2471,7 +2161,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2497,7 +2187,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>261</v>
+        <v>151</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2523,7 +2213,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>262</v>
+        <v>152</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2549,7 +2239,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>263</v>
+        <v>153</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2575,7 +2265,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>264</v>
+        <v>154</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2598,7 +2288,7 @@
         <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>265</v>
+        <v>155</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2624,7 +2314,7 @@
         <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>266</v>
+        <v>156</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2650,7 +2340,7 @@
         <v>115</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>267</v>
+        <v>157</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2676,7 +2366,7 @@
         <v>115</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>268</v>
+        <v>158</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2702,7 +2392,7 @@
         <v>115</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>269</v>
+        <v>159</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2725,7 +2415,7 @@
         <v>115</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2751,7 +2441,7 @@
         <v>115</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>271</v>
+        <v>161</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2777,7 +2467,7 @@
         <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>272</v>
+        <v>162</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2803,7 +2493,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>273</v>
+        <v>163</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2829,7 +2519,7 @@
         <v>115</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>274</v>
+        <v>164</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2858,7 +2548,7 @@
         <v>115</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>275</v>
+        <v>165</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2887,7 +2577,7 @@
         <v>115</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>276</v>
+        <v>166</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -2916,7 +2606,7 @@
         <v>115</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>277</v>
+        <v>167</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2939,7 +2629,7 @@
         <v>115</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>278</v>
+        <v>168</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -2968,7 +2658,7 @@
         <v>115</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>279</v>
+        <v>169</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -2997,7 +2687,7 @@
         <v>115</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>280</v>
+        <v>170</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -3023,7 +2713,7 @@
         <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>281</v>
+        <v>171</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -3052,7 +2742,7 @@
         <v>115</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>282</v>
+        <v>172</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -3084,7 +2774,7 @@
         <v>115</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>283</v>
+        <v>173</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -3113,7 +2803,7 @@
         <v>115</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>284</v>
+        <v>174</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
@@ -3142,7 +2832,7 @@
         <v>115</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>285</v>
+        <v>175</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -3174,7 +2864,7 @@
         <v>115</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -3203,7 +2893,7 @@
         <v>115</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>287</v>
+        <v>177</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
@@ -3232,7 +2922,7 @@
         <v>115</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>288</v>
+        <v>178</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
@@ -3261,7 +2951,7 @@
         <v>115</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>289</v>
+        <v>179</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -3284,7 +2974,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>290</v>
+        <v>180</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -3313,7 +3003,7 @@
         <v>115</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>291</v>
+        <v>181</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
@@ -3342,7 +3032,7 @@
         <v>115</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>292</v>
+        <v>182</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
@@ -3368,7 +3058,7 @@
         <v>115</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>293</v>
+        <v>183</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -3397,7 +3087,7 @@
         <v>115</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>294</v>
+        <v>184</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
@@ -3429,7 +3119,7 @@
         <v>115</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>295</v>
+        <v>185</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -3458,7 +3148,7 @@
         <v>115</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>296</v>
+        <v>186</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
@@ -3487,7 +3177,7 @@
         <v>115</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>297</v>
+        <v>187</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -3519,7 +3209,7 @@
         <v>115</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>298</v>
+        <v>188</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -3548,7 +3238,7 @@
         <v>115</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>299</v>
+        <v>189</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -3577,7 +3267,7 @@
         <v>115</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -3606,7 +3296,7 @@
         <v>115</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>301</v>
+        <v>191</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
@@ -3629,7 +3319,7 @@
         <v>115</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>302</v>
+        <v>192</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -3658,7 +3348,7 @@
         <v>115</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>303</v>
+        <v>193</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3687,7 +3377,7 @@
         <v>115</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>304</v>
+        <v>194</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3713,7 +3403,7 @@
         <v>115</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>305</v>
+        <v>195</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -3742,7 +3432,7 @@
         <v>115</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>306</v>
+        <v>196</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -3774,7 +3464,7 @@
         <v>115</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>307</v>
+        <v>197</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>29</v>
@@ -3803,7 +3493,7 @@
         <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>308</v>
+        <v>198</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>29</v>
@@ -3832,7 +3522,7 @@
         <v>115</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>309</v>
+        <v>199</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>29</v>
@@ -3864,7 +3554,7 @@
         <v>115</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>310</v>
+        <v>200</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>29</v>
@@ -3883,11 +3573,14 @@
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="s">
+        <v>217</v>
+      </c>
       <c r="B54" s="1" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>15</v>
@@ -3930,7 +3623,7 @@
         <v>115</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
@@ -3949,11 +3642,14 @@
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A57" s="1" t="s">
+        <v>217</v>
+      </c>
       <c r="B57" s="1" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>15</v>
@@ -3996,7 +3692,7 @@
         <v>115</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>312</v>
+        <v>202</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
@@ -4015,11 +3711,14 @@
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A60" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="B60" s="1" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>15</v>
@@ -4062,7 +3761,7 @@
         <v>115</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>313</v>
+        <v>203</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>29</v>
@@ -4071,7 +3770,7 @@
         <v>15</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>214</v>
+        <v>117</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>114</v>
@@ -4088,7 +3787,7 @@
         <v>115</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>314</v>
+        <v>204</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>29</v>
@@ -4097,7 +3796,7 @@
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>214</v>
+        <v>117</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>109</v>
@@ -4113,8 +3812,8 @@
       <c r="A64" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B64" t="s" s="1">
-        <v>315</v>
+      <c r="B64" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>29</v>
@@ -4123,7 +3822,7 @@
         <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>214</v>
+        <v>117</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>33</v>
@@ -4150,14 +3849,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -4191,7 +3890,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>317</v>
+        <v>207</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4214,7 +3913,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>318</v>
+        <v>208</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4237,7 +3936,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>319</v>
+        <v>209</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4260,7 +3959,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>320</v>
+        <v>210</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4283,7 +3982,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>321</v>
+        <v>211</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4302,8 +4001,14 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>221</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
@@ -4312,12 +4017,18 @@
         <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>222</v>
+      </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>15</v>
@@ -4326,12 +4037,18 @@
         <v>35</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s">
+        <v>223</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>15</v>
@@ -4340,7 +4057,7 @@
         <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4353,14 +4070,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
-    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4391,7 +4108,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>322</v>
+        <v>212</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4414,7 +4131,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>323</v>
+        <v>213</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4437,7 +4154,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>324</v>
+        <v>214</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4460,7 +4177,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>325</v>
+        <v>215</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4483,7 +4200,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>326</v>
+        <v>216</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4511,12 +4228,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4544,7 +4261,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>316</v>
+        <v>206</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
